--- a/V32.xlsx
+++ b/V32.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c126945bea7d3965/UNI/AP1/GitHub/AP1-Gruppe-143/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{729B160A-1DE6-4DC4-9A8A-4CDF623622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19DC95A1-2364-427F-85F8-53FB3CA7D8E3}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{729B160A-1DE6-4DC4-9A8A-4CDF623622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A524A4C-3AAC-4094-A0BD-386D2B932431}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="3" xr2:uid="{579B69CA-20DC-4D38-A6C3-75478BE869BA}"/>
   </bookViews>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632A092A-0E89-4722-870C-C1B74DD39C8B}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
@@ -473,7 +473,7 @@
         <v>3.6</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C21" si="0">B3/10</f>
+        <f t="shared" ref="C3:C51" si="0">B3/10</f>
         <v>0.36</v>
       </c>
     </row>
@@ -691,6 +691,366 @@
       <c r="C21">
         <f t="shared" si="0"/>
         <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>3.34</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>0.33399999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>3.46</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>3.49</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>0.34900000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>3.57</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>3.55</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>3.58</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>0.35799999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>3.35</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>0.33500000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>3.67</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>0.36699999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>3.68</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>3.64</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>0.36399999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>3.66</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>3.52</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>0.35199999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>3.62</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>3.59</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>0.35899999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3.6</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>3.6</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>3.68</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>3.57</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>3.55</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>3.59</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>0.35899999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>3.62</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>3.66</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>3.59</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>0.35899999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>3.52</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>0.35199999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>3.85</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>3.67</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>0.36699999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>3.65</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>3.7</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>3.61</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>0.36099999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>3.61</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>0.36099999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +1094,7 @@
         <v>0.59</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C11" si="0">B3/A3</f>
+        <f t="shared" ref="C3:C8" si="0">B3/A3</f>
         <v>0.29499999999999998</v>
       </c>
     </row>
@@ -833,11 +1193,11 @@
         <v>1000</v>
       </c>
       <c r="B11">
-        <v>329.7</v>
+        <v>392.7</v>
       </c>
       <c r="C11">
         <f>B11/A11</f>
-        <v>0.32969999999999999</v>
+        <v>0.39269999999999999</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -905,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEDD359-B4BE-4771-80DE-264027AED78A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -919,6 +1279,18 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>600</v>
+      </c>
+      <c r="B2">
+        <v>231.92</v>
+      </c>
+      <c r="C2">
+        <f>B2/A2</f>
+        <v>0.38653333333333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/V32.xlsx
+++ b/V32.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c126945bea7d3965/UNI/AP1/GitHub/AP1-Gruppe-143/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{729B160A-1DE6-4DC4-9A8A-4CDF623622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A524A4C-3AAC-4094-A0BD-386D2B932431}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{729B160A-1DE6-4DC4-9A8A-4CDF623622D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471AF281-6072-4172-9256-0C1795A05CE5}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="3" xr2:uid="{579B69CA-20DC-4D38-A6C3-75478BE869BA}"/>
   </bookViews>
@@ -120,7 +120,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -137,6 +138,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1265,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEDD359-B4BE-4771-80DE-264027AED78A}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1280,15 +1285,113 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.34199999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3.46</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7.32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>50</v>
+      </c>
+      <c r="B7" s="1">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>100</v>
+      </c>
+      <c r="B8" s="1">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>200</v>
+      </c>
+      <c r="B9" s="1">
+        <v>76.36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.38179999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>600</v>
       </c>
-      <c r="B2">
+      <c r="B10" s="1">
         <v>231.92</v>
       </c>
-      <c r="C2">
-        <f>B2/A2</f>
+      <c r="C10" s="1">
         <v>0.38653333333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B11" s="1">
+        <v>371.48</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.37148000000000003</v>
       </c>
     </row>
   </sheetData>
